--- a/references/선행연구_사전사후값_정리.xlsx
+++ b/references/선행연구_사전사후값_정리.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>8주, 주 2회 인터벌(돌려차기 30초/휴식 90초) 추가</t>
+          <t>8주, 정규 수련(주 3회)에 주 2회 인터벌 추가</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>태권도 선수</t>
+          <t>훈련된 태권도 선수</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>약 8주 16회, 기술 특이 인터벌 vs 짧은 질주 인터벌 vs 통제</t>
+          <t>정규훈련(주 3회, 60분) 후 반복 질주(3×10×4초) 또는 반복 발차기 인터벌 추가. 기간 원문 확인</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>두 HIIT 모두 향상, 기술 특이 인터벌이 더 큼</t>
+          <t>두 HIIT 모두 향상, 반복 질주 인터벌(HIITRS)이 더 크고 고른 적응</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>수치·표본 수 원문 확인</t>
+          <t>수치·표본 수·기간 원문 확인</t>
         </is>
       </c>
       <c r="O12" s="16" t="inlineStr">
